--- a/public/refractive-outcomes-analyzer/example-data-sheet.xlsx
+++ b/public/refractive-outcomes-analyzer/example-data-sheet.xlsx
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH421"/>
+  <dimension ref="A1:AJ422"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -957,6 +957,11 @@
       <c r="AF3" s="53" t="n"/>
       <c r="AG3" s="53" t="n"/>
       <c r="AH3" s="53" t="n"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>PRE-OP VISION (optional — unlocks standard graphs)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="33.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -1129,6 +1134,16 @@
           <t>Post_K_Steep_Axis_deg</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Pre_UDVA_logMAR</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Pre_CDVA_logMAR</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="33.75" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
@@ -1299,6 +1314,16 @@
       <c r="AH5" s="15" t="inlineStr">
         <is>
           <t>Axis of the post-op steep meridian (°)</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Pre-op uncorrected VA (logMAR, Snellen 6/60 or 20/200, or decimal)</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Pre-op best-corrected VA — enables efficacy &amp; safety indices, UDVA-vs-CDVA and lines-gained/lost graphs</t>
         </is>
       </c>
     </row>
@@ -1419,6 +1444,12 @@
       <c r="AH6" s="55" t="n">
         <v>71</v>
       </c>
+      <c r="AI6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -1537,6 +1568,12 @@
       <c r="AH7" s="55" t="n">
         <v>10</v>
       </c>
+      <c r="AI7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -1655,6 +1692,12 @@
       <c r="AH8" s="55" t="n">
         <v>64</v>
       </c>
+      <c r="AI8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -1776,6 +1819,12 @@
       </c>
       <c r="AH9" s="55" t="n">
         <v>40</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.66</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1895,6 +1944,12 @@
       <c r="AH10" s="55" t="n">
         <v>80</v>
       </c>
+      <c r="AI10" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.38</v>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -2016,6 +2071,12 @@
       </c>
       <c r="AH11" s="55" t="n">
         <v>127</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -2135,6 +2196,12 @@
       <c r="AH12" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -2253,6 +2320,12 @@
       <c r="AH13" s="55" t="n">
         <v>68</v>
       </c>
+      <c r="AI13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
@@ -2371,6 +2444,12 @@
       <c r="AH14" s="55" t="n">
         <v>114</v>
       </c>
+      <c r="AI14" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -2489,6 +2568,12 @@
       <c r="AH15" s="55" t="n">
         <v>177</v>
       </c>
+      <c r="AI15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
@@ -2611,6 +2696,12 @@
       <c r="AH16" s="55" t="n">
         <v>98</v>
       </c>
+      <c r="AI16" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -2732,6 +2823,12 @@
       </c>
       <c r="AH17" s="55" t="n">
         <v>19</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
@@ -2851,6 +2948,12 @@
       <c r="AH18" s="55" t="n">
         <v>51</v>
       </c>
+      <c r="AI18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -2969,6 +3072,12 @@
       <c r="AH19" s="55" t="n">
         <v>152</v>
       </c>
+      <c r="AI19" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -3087,6 +3196,12 @@
       <c r="AH20" s="55" t="n">
         <v>84</v>
       </c>
+      <c r="AI20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.73</v>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -3205,6 +3320,12 @@
       <c r="AH21" s="55" t="n">
         <v>122</v>
       </c>
+      <c r="AI21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -3323,6 +3444,12 @@
       <c r="AH22" s="55" t="n">
         <v>165</v>
       </c>
+      <c r="AI22" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
@@ -3441,6 +3568,12 @@
       <c r="AH23" s="55" t="n">
         <v>179</v>
       </c>
+      <c r="AI23" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.39</v>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -3559,6 +3692,12 @@
       <c r="AH24" s="55" t="n">
         <v>163</v>
       </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
@@ -3677,6 +3816,12 @@
       <c r="AH25" s="55" t="n">
         <v>125</v>
       </c>
+      <c r="AI25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -3795,6 +3940,12 @@
       <c r="AH26" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI26" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
@@ -3913,6 +4064,12 @@
       <c r="AH27" s="55" t="n">
         <v>175</v>
       </c>
+      <c r="AI27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
@@ -4031,6 +4188,12 @@
       <c r="AH28" s="55" t="n">
         <v>75</v>
       </c>
+      <c r="AI28" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.19</v>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
@@ -4149,6 +4312,12 @@
       <c r="AH29" s="55" t="n">
         <v>132</v>
       </c>
+      <c r="AI29" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
@@ -4267,6 +4436,12 @@
       <c r="AH30" s="55" t="n">
         <v>77</v>
       </c>
+      <c r="AI30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
@@ -4388,6 +4563,12 @@
       </c>
       <c r="AH31" s="55" t="n">
         <v>87</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -4507,6 +4688,12 @@
       <c r="AH32" s="55" t="n">
         <v>113</v>
       </c>
+      <c r="AI32" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
@@ -4625,6 +4812,12 @@
       <c r="AH33" s="55" t="n">
         <v>12</v>
       </c>
+      <c r="AI33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
@@ -4743,6 +4936,12 @@
       <c r="AH34" s="55" t="n">
         <v>82</v>
       </c>
+      <c r="AI34" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="19" t="inlineStr">
@@ -4865,6 +5064,12 @@
       <c r="AH35" s="55" t="n">
         <v>129</v>
       </c>
+      <c r="AI35" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
@@ -4986,6 +5191,12 @@
       </c>
       <c r="AH36" s="55" t="n">
         <v>24</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -5105,6 +5316,12 @@
       <c r="AH37" s="55" t="n">
         <v>168</v>
       </c>
+      <c r="AI37" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
@@ -5223,6 +5440,12 @@
       <c r="AH38" s="55" t="n">
         <v>60</v>
       </c>
+      <c r="AI38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="39" ht="23.25" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -5341,6 +5564,12 @@
       <c r="AH39" s="55" t="n">
         <v>2</v>
       </c>
+      <c r="AI39" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
@@ -5462,6 +5691,12 @@
       </c>
       <c r="AH40" s="55" t="n">
         <v>140</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -5581,6 +5816,12 @@
       <c r="AH41" s="55" t="n">
         <v>62</v>
       </c>
+      <c r="AI41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
@@ -5699,6 +5940,12 @@
       <c r="AH42" s="55" t="n">
         <v>81</v>
       </c>
+      <c r="AI42" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
@@ -5817,6 +6064,12 @@
       <c r="AH43" s="55" t="n">
         <v>140</v>
       </c>
+      <c r="AI43" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
@@ -5939,6 +6192,12 @@
       <c r="AH44" s="55" t="n">
         <v>23</v>
       </c>
+      <c r="AI44" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="19" t="inlineStr">
@@ -6060,6 +6319,12 @@
       </c>
       <c r="AH45" s="55" t="n">
         <v>127</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="46" ht="23.25" customHeight="1">
@@ -6179,6 +6444,12 @@
       <c r="AH46" s="55" t="n">
         <v>171</v>
       </c>
+      <c r="AI46" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="47" ht="23.25" customHeight="1">
       <c r="A47" s="19" t="inlineStr">
@@ -6297,6 +6568,12 @@
       <c r="AH47" s="55" t="n">
         <v>3</v>
       </c>
+      <c r="AI47" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
@@ -6415,6 +6692,12 @@
       <c r="AH48" s="55" t="n">
         <v>62</v>
       </c>
+      <c r="AI48" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="19" t="inlineStr">
@@ -6533,6 +6816,12 @@
       <c r="AH49" s="55" t="n">
         <v>70</v>
       </c>
+      <c r="AI49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.74</v>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
@@ -6651,6 +6940,12 @@
       <c r="AH50" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI50" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="19" t="inlineStr">
@@ -6769,6 +7064,12 @@
       <c r="AH51" s="55" t="n">
         <v>63</v>
       </c>
+      <c r="AI51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="52" ht="23.25" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
@@ -6887,6 +7188,12 @@
       <c r="AH52" s="55" t="n">
         <v>159</v>
       </c>
+      <c r="AI52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="19" t="inlineStr">
@@ -7005,6 +7312,12 @@
       <c r="AH53" s="55" t="n">
         <v>32</v>
       </c>
+      <c r="AI53" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
@@ -7126,6 +7439,12 @@
       </c>
       <c r="AH54" s="55" t="n">
         <v>139</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -7245,6 +7564,12 @@
       <c r="AH55" s="55" t="n">
         <v>132</v>
       </c>
+      <c r="AI55" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0.6899999999999999</v>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
@@ -7363,6 +7688,12 @@
       <c r="AH56" s="55" t="n">
         <v>109</v>
       </c>
+      <c r="AI56" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0.39</v>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="19" t="inlineStr">
@@ -7481,6 +7812,12 @@
       <c r="AH57" s="55" t="n">
         <v>116</v>
       </c>
+      <c r="AI57" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="58" ht="23.25" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
@@ -7599,6 +7936,12 @@
       <c r="AH58" s="55" t="n">
         <v>162</v>
       </c>
+      <c r="AI58" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="59" ht="23.25" customHeight="1">
       <c r="A59" s="19" t="inlineStr">
@@ -7720,6 +8063,12 @@
       </c>
       <c r="AH59" s="55" t="n">
         <v>98</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -7839,6 +8188,12 @@
       <c r="AH60" s="55" t="n">
         <v>89</v>
       </c>
+      <c r="AI60" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="19" t="inlineStr">
@@ -7957,6 +8312,12 @@
       <c r="AH61" s="55" t="n">
         <v>159</v>
       </c>
+      <c r="AI61" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
@@ -8075,6 +8436,12 @@
       <c r="AH62" s="55" t="n">
         <v>51</v>
       </c>
+      <c r="AI62" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0.43</v>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="19" t="inlineStr">
@@ -8193,6 +8560,12 @@
       <c r="AH63" s="55" t="n">
         <v>69</v>
       </c>
+      <c r="AI63" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
@@ -8311,6 +8684,12 @@
       <c r="AH64" s="55" t="n">
         <v>87</v>
       </c>
+      <c r="AI64" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="19" t="inlineStr">
@@ -8432,6 +8811,12 @@
       </c>
       <c r="AH65" s="55" t="n">
         <v>2</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="66" ht="23.25" customHeight="1">
@@ -8551,6 +8936,12 @@
       <c r="AH66" s="55" t="n">
         <v>73</v>
       </c>
+      <c r="AI66" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="67" ht="23.25" customHeight="1">
       <c r="A67" s="19" t="inlineStr">
@@ -8673,6 +9064,12 @@
       <c r="AH67" s="55" t="n">
         <v>72</v>
       </c>
+      <c r="AI67" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
@@ -8794,6 +9191,12 @@
       </c>
       <c r="AH68" s="55" t="n">
         <v>94</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
@@ -8913,6 +9316,12 @@
       <c r="AH69" s="55" t="n">
         <v>39</v>
       </c>
+      <c r="AI69" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
@@ -9031,6 +9440,12 @@
       <c r="AH70" s="55" t="n">
         <v>124</v>
       </c>
+      <c r="AI70" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="19" t="inlineStr">
@@ -9153,6 +9568,12 @@
       <c r="AH71" s="55" t="n">
         <v>93</v>
       </c>
+      <c r="AI71" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
@@ -9274,6 +9695,12 @@
       </c>
       <c r="AH72" s="55" t="n">
         <v>109</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
@@ -9393,6 +9820,12 @@
       <c r="AH73" s="55" t="n">
         <v>110</v>
       </c>
+      <c r="AI73" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
@@ -9511,6 +9944,12 @@
       <c r="AH74" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI74" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0.19</v>
+      </c>
     </row>
     <row r="75" ht="23.25" customHeight="1">
       <c r="A75" s="19" t="inlineStr">
@@ -9629,6 +10068,12 @@
       <c r="AH75" s="55" t="n">
         <v>122</v>
       </c>
+      <c r="AI75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>0.57</v>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
@@ -9747,6 +10192,12 @@
       <c r="AH76" s="55" t="n">
         <v>53</v>
       </c>
+      <c r="AI76" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="19" t="inlineStr">
@@ -9865,6 +10316,12 @@
       <c r="AH77" s="55" t="n">
         <v>81</v>
       </c>
+      <c r="AI77" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
@@ -9986,6 +10443,12 @@
       </c>
       <c r="AH78" s="55" t="n">
         <v>54</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="79" ht="23.25" customHeight="1">
@@ -10105,6 +10568,12 @@
       <c r="AH79" s="55" t="n">
         <v>171</v>
       </c>
+      <c r="AI79" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
@@ -10223,6 +10692,12 @@
       <c r="AH80" s="55" t="n">
         <v>23</v>
       </c>
+      <c r="AI80" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="19" t="inlineStr">
@@ -10344,6 +10819,12 @@
       </c>
       <c r="AH81" s="55" t="n">
         <v>52</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
@@ -10463,6 +10944,12 @@
       <c r="AH82" s="55" t="n">
         <v>149</v>
       </c>
+      <c r="AI82" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>0.39</v>
+      </c>
     </row>
     <row r="83" ht="23.25" customHeight="1">
       <c r="A83" s="19" t="inlineStr">
@@ -10581,6 +11068,12 @@
       <c r="AH83" s="55" t="n">
         <v>140</v>
       </c>
+      <c r="AI83" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
@@ -10702,6 +11195,12 @@
       </c>
       <c r="AH84" s="55" t="n">
         <v>67</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -10821,6 +11320,12 @@
       <c r="AH85" s="55" t="n">
         <v>81</v>
       </c>
+      <c r="AI85" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
@@ -10939,6 +11444,12 @@
       <c r="AH86" s="55" t="n">
         <v>41</v>
       </c>
+      <c r="AI86" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>0.19</v>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="19" t="inlineStr">
@@ -11060,6 +11571,12 @@
       </c>
       <c r="AH87" s="55" t="n">
         <v>92</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
@@ -11179,6 +11696,12 @@
       <c r="AH88" s="55" t="n">
         <v>179</v>
       </c>
+      <c r="AI88" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="89" ht="23.25" customHeight="1">
       <c r="A89" s="19" t="inlineStr">
@@ -11297,6 +11820,12 @@
       <c r="AH89" s="55" t="n">
         <v>93</v>
       </c>
+      <c r="AI89" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="16" t="inlineStr">
@@ -11415,6 +11944,12 @@
       <c r="AH90" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI90" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="19" t="inlineStr">
@@ -11533,6 +12068,12 @@
       <c r="AH91" s="55" t="n">
         <v>164</v>
       </c>
+      <c r="AI91" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="16" t="inlineStr">
@@ -11651,6 +12192,12 @@
       <c r="AH92" s="55" t="n">
         <v>22</v>
       </c>
+      <c r="AI92" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="19" t="inlineStr">
@@ -11769,6 +12316,12 @@
       <c r="AH93" s="55" t="n">
         <v>103</v>
       </c>
+      <c r="AI93" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="16" t="inlineStr">
@@ -11887,6 +12440,12 @@
       <c r="AH94" s="55" t="n">
         <v>73</v>
       </c>
+      <c r="AI94" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="19" t="inlineStr">
@@ -12005,6 +12564,12 @@
       <c r="AH95" s="55" t="n">
         <v>16</v>
       </c>
+      <c r="AI95" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>0.38</v>
+      </c>
     </row>
     <row r="96" ht="23.25" customHeight="1">
       <c r="A96" s="16" t="inlineStr">
@@ -12123,6 +12688,12 @@
       <c r="AH96" s="55" t="n">
         <v>95</v>
       </c>
+      <c r="AI96" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="97" ht="23.25" customHeight="1">
       <c r="A97" s="19" t="inlineStr">
@@ -12241,6 +12812,12 @@
       <c r="AH97" s="55" t="n">
         <v>2</v>
       </c>
+      <c r="AI97" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>0.6899999999999999</v>
+      </c>
     </row>
     <row r="98" ht="23.25" customHeight="1">
       <c r="A98" s="16" t="inlineStr">
@@ -12363,6 +12940,12 @@
       <c r="AH98" s="55" t="n">
         <v>64</v>
       </c>
+      <c r="AI98" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="19" t="inlineStr">
@@ -12484,6 +13067,12 @@
       </c>
       <c r="AH99" s="55" t="n">
         <v>40</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -12603,6 +13192,12 @@
       <c r="AH100" s="55" t="n">
         <v>161</v>
       </c>
+      <c r="AI100" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="19" t="inlineStr">
@@ -12721,6 +13316,12 @@
       <c r="AH101" s="55" t="n">
         <v>62</v>
       </c>
+      <c r="AI101" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="16" t="inlineStr">
@@ -12839,6 +13440,12 @@
       <c r="AH102" s="55" t="n">
         <v>27</v>
       </c>
+      <c r="AI102" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="19" t="inlineStr">
@@ -12957,6 +13564,12 @@
       <c r="AH103" s="55" t="n">
         <v>158</v>
       </c>
+      <c r="AI103" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="16" t="inlineStr">
@@ -13075,6 +13688,12 @@
       <c r="AH104" s="55" t="n">
         <v>98</v>
       </c>
+      <c r="AI104" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="19" t="inlineStr">
@@ -13193,6 +13812,12 @@
       <c r="AH105" s="55" t="n">
         <v>82</v>
       </c>
+      <c r="AI105" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="106" ht="23.25" customHeight="1">
       <c r="A106" s="16" t="inlineStr">
@@ -13311,6 +13936,12 @@
       <c r="AH106" s="55" t="n">
         <v>153</v>
       </c>
+      <c r="AI106" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>0.6899999999999999</v>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="19" t="inlineStr">
@@ -13429,6 +14060,12 @@
       <c r="AH107" s="55" t="n">
         <v>118</v>
       </c>
+      <c r="AI107" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="16" t="inlineStr">
@@ -13547,6 +14184,12 @@
       <c r="AH108" s="55" t="n">
         <v>80</v>
       </c>
+      <c r="AI108" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="19" t="inlineStr">
@@ -13665,6 +14308,12 @@
       <c r="AH109" s="55" t="n">
         <v>79</v>
       </c>
+      <c r="AI109" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="110" ht="23.25" customHeight="1">
       <c r="A110" s="22" t="inlineStr">
@@ -13783,6 +14432,12 @@
       <c r="AH110" s="55" t="n">
         <v>97</v>
       </c>
+      <c r="AI110" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="111" ht="23.25" customHeight="1">
       <c r="A111" s="25" t="inlineStr">
@@ -13904,6 +14559,12 @@
       </c>
       <c r="AH111" s="55" t="n">
         <v>36</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
@@ -14023,6 +14684,12 @@
       <c r="AH112" s="55" t="n">
         <v>92</v>
       </c>
+      <c r="AI112" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="25" t="inlineStr">
@@ -14141,6 +14808,12 @@
       <c r="AH113" s="55" t="n">
         <v>72</v>
       </c>
+      <c r="AI113" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="114" ht="23.25" customHeight="1">
       <c r="A114" s="22" t="inlineStr">
@@ -14259,6 +14932,12 @@
       <c r="AH114" s="55" t="n">
         <v>141</v>
       </c>
+      <c r="AI114" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="25" t="inlineStr">
@@ -14377,6 +15056,12 @@
       <c r="AH115" s="55" t="n">
         <v>139</v>
       </c>
+      <c r="AI115" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="22" t="inlineStr">
@@ -14495,6 +15180,12 @@
       <c r="AH116" s="55" t="n">
         <v>92</v>
       </c>
+      <c r="AI116" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="117" ht="23.25" customHeight="1">
       <c r="A117" s="25" t="inlineStr">
@@ -14613,6 +15304,12 @@
       <c r="AH117" s="55" t="n">
         <v>3</v>
       </c>
+      <c r="AI117" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="22" t="inlineStr">
@@ -14731,6 +15428,12 @@
       <c r="AH118" s="55" t="n">
         <v>179</v>
       </c>
+      <c r="AI118" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="25" t="inlineStr">
@@ -14849,6 +15552,12 @@
       <c r="AH119" s="55" t="n">
         <v>115</v>
       </c>
+      <c r="AI119" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="22" t="inlineStr">
@@ -14967,6 +15676,12 @@
       <c r="AH120" s="55" t="n">
         <v>175</v>
       </c>
+      <c r="AI120" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="25" t="inlineStr">
@@ -15085,6 +15800,12 @@
       <c r="AH121" s="55" t="n">
         <v>109</v>
       </c>
+      <c r="AI121" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.19</v>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="22" t="inlineStr">
@@ -15203,6 +15924,12 @@
       <c r="AH122" s="55" t="n">
         <v>120</v>
       </c>
+      <c r="AI122" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="25" t="inlineStr">
@@ -15321,6 +16048,12 @@
       <c r="AH123" s="55" t="n">
         <v>34</v>
       </c>
+      <c r="AI123" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="22" t="inlineStr">
@@ -15439,6 +16172,12 @@
       <c r="AH124" s="55" t="n">
         <v>46</v>
       </c>
+      <c r="AI124" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="25" t="inlineStr">
@@ -15557,6 +16296,12 @@
       <c r="AH125" s="55" t="n">
         <v>7</v>
       </c>
+      <c r="AI125" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="22" t="inlineStr">
@@ -15675,6 +16420,12 @@
       <c r="AH126" s="55" t="n">
         <v>178</v>
       </c>
+      <c r="AI126" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="25" t="inlineStr">
@@ -15793,6 +16544,12 @@
       <c r="AH127" s="55" t="n">
         <v>36</v>
       </c>
+      <c r="AI127" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="22" t="inlineStr">
@@ -15914,6 +16671,12 @@
       </c>
       <c r="AH128" s="55" t="n">
         <v>17</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="129">
@@ -16033,6 +16796,12 @@
       <c r="AH129" s="55" t="n">
         <v>115</v>
       </c>
+      <c r="AI129" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="22" t="inlineStr">
@@ -16151,6 +16920,12 @@
       <c r="AH130" s="55" t="n">
         <v>118</v>
       </c>
+      <c r="AI130" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="25" t="inlineStr">
@@ -16269,6 +17044,12 @@
       <c r="AH131" s="55" t="n">
         <v>61</v>
       </c>
+      <c r="AI131" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="22" t="inlineStr">
@@ -16387,6 +17168,12 @@
       <c r="AH132" s="55" t="n">
         <v>164</v>
       </c>
+      <c r="AI132" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.19</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="25" t="inlineStr">
@@ -16505,6 +17292,12 @@
       <c r="AH133" s="55" t="n">
         <v>74</v>
       </c>
+      <c r="AI133" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="22" t="inlineStr">
@@ -16623,6 +17416,12 @@
       <c r="AH134" s="55" t="n">
         <v>32</v>
       </c>
+      <c r="AI134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="25" t="inlineStr">
@@ -16741,6 +17540,12 @@
       <c r="AH135" s="55" t="n">
         <v>127</v>
       </c>
+      <c r="AI135" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="22" t="inlineStr">
@@ -16859,6 +17664,12 @@
       <c r="AH136" s="55" t="n">
         <v>116</v>
       </c>
+      <c r="AI136" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="25" t="inlineStr">
@@ -16977,6 +17788,12 @@
       <c r="AH137" s="55" t="n">
         <v>176</v>
       </c>
+      <c r="AI137" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="22" t="inlineStr">
@@ -17095,6 +17912,12 @@
       <c r="AH138" s="55" t="n">
         <v>97</v>
       </c>
+      <c r="AI138" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="25" t="inlineStr">
@@ -17213,6 +18036,12 @@
       <c r="AH139" s="55" t="n">
         <v>92</v>
       </c>
+      <c r="AI139" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="22" t="inlineStr">
@@ -17331,6 +18160,12 @@
       <c r="AH140" s="55" t="n">
         <v>144</v>
       </c>
+      <c r="AI140" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="25" t="inlineStr">
@@ -17449,6 +18284,12 @@
       <c r="AH141" s="55" t="n">
         <v>29</v>
       </c>
+      <c r="AI141" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="22" t="inlineStr">
@@ -17567,6 +18408,12 @@
       <c r="AH142" s="55" t="n">
         <v>78</v>
       </c>
+      <c r="AI142" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="25" t="inlineStr">
@@ -17685,6 +18532,12 @@
       <c r="AH143" s="55" t="n">
         <v>92</v>
       </c>
+      <c r="AI143" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="22" t="inlineStr">
@@ -17803,6 +18656,12 @@
       <c r="AH144" s="55" t="n">
         <v>26</v>
       </c>
+      <c r="AI144" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="25" t="inlineStr">
@@ -17921,6 +18780,12 @@
       <c r="AH145" s="55" t="n">
         <v>73</v>
       </c>
+      <c r="AI145" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="22" t="inlineStr">
@@ -18039,6 +18904,12 @@
       <c r="AH146" s="55" t="n">
         <v>49</v>
       </c>
+      <c r="AI146" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="25" t="inlineStr">
@@ -18157,6 +19028,12 @@
       <c r="AH147" s="55" t="n">
         <v>41</v>
       </c>
+      <c r="AI147" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="22" t="inlineStr">
@@ -18275,6 +19152,12 @@
       <c r="AH148" s="55" t="n">
         <v>109</v>
       </c>
+      <c r="AI148" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="25" t="inlineStr">
@@ -18396,6 +19279,12 @@
       </c>
       <c r="AH149" s="55" t="n">
         <v>155</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="150">
@@ -18515,6 +19404,12 @@
       <c r="AH150" s="55" t="n">
         <v>130</v>
       </c>
+      <c r="AI150" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="25" t="inlineStr">
@@ -18633,6 +19528,12 @@
       <c r="AH151" s="55" t="n">
         <v>39</v>
       </c>
+      <c r="AI151" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="22" t="inlineStr">
@@ -18751,6 +19652,12 @@
       <c r="AH152" s="55" t="n">
         <v>69</v>
       </c>
+      <c r="AI152" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="25" t="inlineStr">
@@ -18869,6 +19776,12 @@
       <c r="AH153" s="55" t="n">
         <v>91</v>
       </c>
+      <c r="AI153" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="22" t="inlineStr">
@@ -18991,6 +19904,12 @@
       <c r="AH154" s="55" t="n">
         <v>137</v>
       </c>
+      <c r="AI154" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>0.39</v>
+      </c>
     </row>
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="25" t="inlineStr">
@@ -19112,6 +20031,12 @@
       </c>
       <c r="AH155" s="55" t="n">
         <v>101</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="156">
@@ -19231,6 +20156,12 @@
       <c r="AH156" s="55" t="n">
         <v>54</v>
       </c>
+      <c r="AI156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="25" t="inlineStr">
@@ -19349,6 +20280,12 @@
       <c r="AH157" s="55" t="n">
         <v>38</v>
       </c>
+      <c r="AI157" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="22" t="inlineStr">
@@ -19467,6 +20404,12 @@
       <c r="AH158" s="55" t="n">
         <v>38</v>
       </c>
+      <c r="AI158" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="25" t="inlineStr">
@@ -19585,6 +20528,12 @@
       <c r="AH159" s="55" t="n">
         <v>116</v>
       </c>
+      <c r="AI159" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="22" t="inlineStr">
@@ -19703,6 +20652,12 @@
       <c r="AH160" s="55" t="n">
         <v>125</v>
       </c>
+      <c r="AI160" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="25" t="inlineStr">
@@ -19824,6 +20779,12 @@
       </c>
       <c r="AH161" s="55" t="n">
         <v>176</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>0.66</v>
       </c>
     </row>
     <row r="162">
@@ -19943,6 +20904,12 @@
       <c r="AH162" s="55" t="n">
         <v>101</v>
       </c>
+      <c r="AI162" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="25" t="inlineStr">
@@ -20061,6 +21028,12 @@
       <c r="AH163" s="55" t="n">
         <v>16</v>
       </c>
+      <c r="AI163" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="22" t="inlineStr">
@@ -20179,6 +21152,12 @@
       <c r="AH164" s="55" t="n">
         <v>153</v>
       </c>
+      <c r="AI164" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="25" t="inlineStr">
@@ -20297,6 +21276,12 @@
       <c r="AH165" s="55" t="n">
         <v>67</v>
       </c>
+      <c r="AI165" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="22" t="inlineStr">
@@ -20415,6 +21400,12 @@
       <c r="AH166" s="55" t="n">
         <v>161</v>
       </c>
+      <c r="AI166" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="25" t="inlineStr">
@@ -20536,6 +21527,12 @@
       </c>
       <c r="AH167" s="55" t="n">
         <v>176</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="168">
@@ -20655,6 +21652,12 @@
       <c r="AH168" s="55" t="n">
         <v>19</v>
       </c>
+      <c r="AI168" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="25" t="inlineStr">
@@ -20773,6 +21776,12 @@
       <c r="AH169" s="55" t="n">
         <v>104</v>
       </c>
+      <c r="AI169" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="22" t="inlineStr">
@@ -20891,6 +21900,12 @@
       <c r="AH170" s="55" t="n">
         <v>125</v>
       </c>
+      <c r="AI170" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="25" t="inlineStr">
@@ -21012,6 +22027,12 @@
       </c>
       <c r="AH171" s="55" t="n">
         <v>65</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="172">
@@ -21131,6 +22152,12 @@
       <c r="AH172" s="55" t="n">
         <v>134</v>
       </c>
+      <c r="AI172" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="25" t="inlineStr">
@@ -21249,6 +22276,12 @@
       <c r="AH173" s="55" t="n">
         <v>168</v>
       </c>
+      <c r="AI173" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="22" t="inlineStr">
@@ -21367,6 +22400,12 @@
       <c r="AH174" s="55" t="n">
         <v>171</v>
       </c>
+      <c r="AI174" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="25" t="inlineStr">
@@ -21485,6 +22524,12 @@
       <c r="AH175" s="55" t="n">
         <v>16</v>
       </c>
+      <c r="AI175" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="22" t="inlineStr">
@@ -21603,6 +22648,12 @@
       <c r="AH176" s="55" t="n">
         <v>29</v>
       </c>
+      <c r="AI176" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="25" t="inlineStr">
@@ -21721,6 +22772,12 @@
       <c r="AH177" s="55" t="n">
         <v>14</v>
       </c>
+      <c r="AI177" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="22" t="inlineStr">
@@ -21839,6 +22896,12 @@
       <c r="AH178" s="55" t="n">
         <v>128</v>
       </c>
+      <c r="AI178" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="25" t="inlineStr">
@@ -21957,6 +23020,12 @@
       <c r="AH179" s="55" t="n">
         <v>96</v>
       </c>
+      <c r="AI179" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="22" t="inlineStr">
@@ -22075,6 +23144,12 @@
       <c r="AH180" s="55" t="n">
         <v>122</v>
       </c>
+      <c r="AI180" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="25" t="inlineStr">
@@ -22193,6 +23268,12 @@
       <c r="AH181" s="55" t="n">
         <v>87</v>
       </c>
+      <c r="AI181" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>0.73</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="22" t="inlineStr">
@@ -22311,6 +23392,12 @@
       <c r="AH182" s="55" t="n">
         <v>115</v>
       </c>
+      <c r="AI182" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="25" t="inlineStr">
@@ -22429,6 +23516,12 @@
       <c r="AH183" s="55" t="n">
         <v>75</v>
       </c>
+      <c r="AI183" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="22" t="inlineStr">
@@ -22547,6 +23640,12 @@
       <c r="AH184" s="55" t="n">
         <v>155</v>
       </c>
+      <c r="AI184" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="25" t="inlineStr">
@@ -22668,6 +23767,12 @@
       </c>
       <c r="AH185" s="55" t="n">
         <v>39</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="186">
@@ -22787,6 +23892,12 @@
       <c r="AH186" s="55" t="n">
         <v>8</v>
       </c>
+      <c r="AI186" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="25" t="inlineStr">
@@ -22908,6 +24019,12 @@
       </c>
       <c r="AH187" s="55" t="n">
         <v>75</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="188">
@@ -23027,6 +24144,12 @@
       <c r="AH188" s="55" t="n">
         <v>93</v>
       </c>
+      <c r="AI188" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="25" t="inlineStr">
@@ -23145,6 +24268,12 @@
       <c r="AH189" s="55" t="n">
         <v>143</v>
       </c>
+      <c r="AI189" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="22" t="inlineStr">
@@ -23263,6 +24392,12 @@
       <c r="AH190" s="55" t="n">
         <v>124</v>
       </c>
+      <c r="AI190" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="25" t="inlineStr">
@@ -23381,6 +24516,12 @@
       <c r="AH191" s="55" t="n">
         <v>86</v>
       </c>
+      <c r="AI191" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="22" t="inlineStr">
@@ -23499,6 +24640,12 @@
       <c r="AH192" s="55" t="n">
         <v>132</v>
       </c>
+      <c r="AI192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="25" t="inlineStr">
@@ -23617,6 +24764,12 @@
       <c r="AH193" s="55" t="n">
         <v>7</v>
       </c>
+      <c r="AI193" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>0.43</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="22" t="inlineStr">
@@ -23735,6 +24888,12 @@
       <c r="AH194" s="55" t="n">
         <v>63</v>
       </c>
+      <c r="AI194" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="25" t="inlineStr">
@@ -23853,6 +25012,12 @@
       <c r="AH195" s="55" t="n">
         <v>94</v>
       </c>
+      <c r="AI195" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="22" t="inlineStr">
@@ -23971,6 +25136,12 @@
       <c r="AH196" s="55" t="n">
         <v>130</v>
       </c>
+      <c r="AI196" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="25" t="inlineStr">
@@ -24089,6 +25260,12 @@
       <c r="AH197" s="55" t="n">
         <v>143</v>
       </c>
+      <c r="AI197" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="22" t="inlineStr">
@@ -24207,6 +25384,12 @@
       <c r="AH198" s="55" t="n">
         <v>96</v>
       </c>
+      <c r="AI198" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="25" t="inlineStr">
@@ -24325,6 +25508,12 @@
       <c r="AH199" s="55" t="n">
         <v>137</v>
       </c>
+      <c r="AI199" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="22" t="inlineStr">
@@ -24443,6 +25632,12 @@
       <c r="AH200" s="55" t="n">
         <v>119</v>
       </c>
+      <c r="AI200" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="25" t="inlineStr">
@@ -24561,6 +25756,12 @@
       <c r="AH201" s="55" t="n">
         <v>100</v>
       </c>
+      <c r="AI201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="22" t="inlineStr">
@@ -24679,6 +25880,12 @@
       <c r="AH202" s="55" t="n">
         <v>154</v>
       </c>
+      <c r="AI202" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>0.43</v>
+      </c>
     </row>
     <row r="203" ht="28" customHeight="1">
       <c r="A203" s="25" t="inlineStr">
@@ -24800,6 +26007,12 @@
       </c>
       <c r="AH203" s="55" t="n">
         <v>80</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="204">
@@ -24919,6 +26132,12 @@
       <c r="AH204" s="55" t="n">
         <v>159</v>
       </c>
+      <c r="AI204" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="25" t="inlineStr">
@@ -25037,6 +26256,12 @@
       <c r="AH205" s="55" t="n">
         <v>108</v>
       </c>
+      <c r="AI205" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="22" t="inlineStr">
@@ -25155,6 +26380,12 @@
       <c r="AH206" s="55" t="n">
         <v>126</v>
       </c>
+      <c r="AI206" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="25" t="inlineStr">
@@ -25273,6 +26504,12 @@
       <c r="AH207" s="55" t="n">
         <v>132</v>
       </c>
+      <c r="AI207" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="22" t="inlineStr">
@@ -25391,6 +26628,12 @@
       <c r="AH208" s="55" t="n">
         <v>132</v>
       </c>
+      <c r="AI208" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="25" t="inlineStr">
@@ -25513,6 +26756,12 @@
       <c r="AH209" s="55" t="n">
         <v>11</v>
       </c>
+      <c r="AI209" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="22" t="inlineStr">
@@ -25634,6 +26883,12 @@
       </c>
       <c r="AH210" s="55" t="n">
         <v>107</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="211">
@@ -25753,6 +27008,12 @@
       <c r="AH211" s="55" t="n">
         <v>28</v>
       </c>
+      <c r="AI211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="22" t="inlineStr">
@@ -25871,6 +27132,12 @@
       <c r="AH212" s="55" t="n">
         <v>83</v>
       </c>
+      <c r="AI212" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="25" t="inlineStr">
@@ -25992,6 +27259,12 @@
       </c>
       <c r="AH213" s="55" t="n">
         <v>143</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="214">
@@ -26107,6 +27380,12 @@
       <c r="AH214" s="55" t="n">
         <v>104</v>
       </c>
+      <c r="AI214" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="31" t="inlineStr">
@@ -26221,6 +27500,12 @@
       <c r="AH215" s="55" t="n">
         <v>28</v>
       </c>
+      <c r="AI215" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="28" t="inlineStr">
@@ -26335,6 +27620,12 @@
       <c r="AH216" s="55" t="n">
         <v>31</v>
       </c>
+      <c r="AI216" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>0.43</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="31" t="inlineStr">
@@ -26449,6 +27740,12 @@
       <c r="AH217" s="55" t="n">
         <v>18</v>
       </c>
+      <c r="AI217" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="28" t="inlineStr">
@@ -26563,6 +27860,12 @@
       <c r="AH218" s="55" t="n">
         <v>160</v>
       </c>
+      <c r="AI218" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="31" t="inlineStr">
@@ -26677,6 +27980,12 @@
       <c r="AH219" s="55" t="n">
         <v>0</v>
       </c>
+      <c r="AI219" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="28" t="inlineStr">
@@ -26791,6 +28100,12 @@
       <c r="AH220" s="55" t="n">
         <v>139</v>
       </c>
+      <c r="AI220" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="31" t="inlineStr">
@@ -26905,6 +28220,12 @@
       <c r="AH221" s="55" t="n">
         <v>151</v>
       </c>
+      <c r="AI221" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="28" t="inlineStr">
@@ -27019,6 +28340,12 @@
       <c r="AH222" s="55" t="n">
         <v>79</v>
       </c>
+      <c r="AI222" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="31" t="inlineStr">
@@ -27133,6 +28460,12 @@
       <c r="AH223" s="55" t="n">
         <v>59</v>
       </c>
+      <c r="AI223" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="28" t="inlineStr">
@@ -27247,6 +28580,12 @@
       <c r="AH224" s="55" t="n">
         <v>120</v>
       </c>
+      <c r="AI224" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>0.38</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="31" t="inlineStr">
@@ -27361,6 +28700,12 @@
       <c r="AH225" s="55" t="n">
         <v>127</v>
       </c>
+      <c r="AI225" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>0.43</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="28" t="inlineStr">
@@ -27478,6 +28823,12 @@
       </c>
       <c r="AH226" s="55" t="n">
         <v>34</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="227">
@@ -27593,6 +28944,12 @@
       <c r="AH227" s="55" t="n">
         <v>84</v>
       </c>
+      <c r="AI227" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="28" t="inlineStr">
@@ -27707,6 +29064,12 @@
       <c r="AH228" s="55" t="n">
         <v>53</v>
       </c>
+      <c r="AI228" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>1.01</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="31" t="inlineStr">
@@ -27821,6 +29184,12 @@
       <c r="AH229" s="55" t="n">
         <v>161</v>
       </c>
+      <c r="AI229" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="28" t="inlineStr">
@@ -27935,6 +29304,12 @@
       <c r="AH230" s="55" t="n">
         <v>63</v>
       </c>
+      <c r="AI230" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="31" t="inlineStr">
@@ -28049,6 +29424,12 @@
       <c r="AH231" s="55" t="n">
         <v>169</v>
       </c>
+      <c r="AI231" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="28" t="inlineStr">
@@ -28167,6 +29548,12 @@
       <c r="AH232" s="55" t="n">
         <v>97</v>
       </c>
+      <c r="AI232" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="233" ht="28" customHeight="1">
       <c r="A233" s="31" t="inlineStr">
@@ -28284,6 +29671,12 @@
       </c>
       <c r="AH233" s="55" t="n">
         <v>28</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="234">
@@ -28399,6 +29792,12 @@
       <c r="AH234" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI234" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="31" t="inlineStr">
@@ -28513,6 +29912,12 @@
       <c r="AH235" s="55" t="n">
         <v>81</v>
       </c>
+      <c r="AI235" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="236" ht="28" customHeight="1">
       <c r="A236" s="28" t="inlineStr">
@@ -28630,6 +30035,12 @@
       </c>
       <c r="AH236" s="55" t="n">
         <v>38</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="237">
@@ -28745,6 +30156,12 @@
       <c r="AH237" s="55" t="n">
         <v>162</v>
       </c>
+      <c r="AI237" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>0.34</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="28" t="inlineStr">
@@ -28859,6 +30276,12 @@
       <c r="AH238" s="55" t="n">
         <v>42</v>
       </c>
+      <c r="AI238" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="31" t="inlineStr">
@@ -28973,6 +30396,12 @@
       <c r="AH239" s="55" t="n">
         <v>94</v>
       </c>
+      <c r="AI239" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="28" t="inlineStr">
@@ -29087,6 +30516,12 @@
       <c r="AH240" s="55" t="n">
         <v>108</v>
       </c>
+      <c r="AI240" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="31" t="inlineStr">
@@ -29201,6 +30636,12 @@
       <c r="AH241" s="55" t="n">
         <v>6</v>
       </c>
+      <c r="AI241" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="242" ht="28" customHeight="1">
       <c r="A242" s="28" t="inlineStr">
@@ -29318,6 +30759,12 @@
       </c>
       <c r="AH242" s="55" t="n">
         <v>96</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="243">
@@ -29433,6 +30880,12 @@
       <c r="AH243" s="55" t="n">
         <v>3</v>
       </c>
+      <c r="AI243" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="28" t="inlineStr">
@@ -29547,6 +31000,12 @@
       <c r="AH244" s="55" t="n">
         <v>132</v>
       </c>
+      <c r="AI244" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>0.73</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="31" t="inlineStr">
@@ -29661,6 +31120,12 @@
       <c r="AH245" s="55" t="n">
         <v>101</v>
       </c>
+      <c r="AI245" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="28" t="inlineStr">
@@ -29778,6 +31243,12 @@
       </c>
       <c r="AH246" s="55" t="n">
         <v>10</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="247">
@@ -29893,6 +31364,12 @@
       <c r="AH247" s="55" t="n">
         <v>63</v>
       </c>
+      <c r="AI247" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="28" t="inlineStr">
@@ -30007,6 +31484,12 @@
       <c r="AH248" s="55" t="n">
         <v>28</v>
       </c>
+      <c r="AI248" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="31" t="inlineStr">
@@ -30124,6 +31607,12 @@
       </c>
       <c r="AH249" s="55" t="n">
         <v>156</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="250">
@@ -30239,6 +31728,12 @@
       <c r="AH250" s="55" t="n">
         <v>144</v>
       </c>
+      <c r="AI250" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="31" t="inlineStr">
@@ -30353,6 +31848,12 @@
       <c r="AH251" s="55" t="n">
         <v>83</v>
       </c>
+      <c r="AI251" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="28" t="inlineStr">
@@ -30467,6 +31968,12 @@
       <c r="AH252" s="55" t="n">
         <v>123</v>
       </c>
+      <c r="AI252" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="31" t="inlineStr">
@@ -30581,6 +32088,12 @@
       <c r="AH253" s="55" t="n">
         <v>142</v>
       </c>
+      <c r="AI253" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="28" t="inlineStr">
@@ -30695,6 +32208,12 @@
       <c r="AH254" s="55" t="n">
         <v>131</v>
       </c>
+      <c r="AI254" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="31" t="inlineStr">
@@ -30812,6 +32331,12 @@
       </c>
       <c r="AH255" s="55" t="n">
         <v>98</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="256">
@@ -30927,6 +32452,12 @@
       <c r="AH256" s="55" t="n">
         <v>6</v>
       </c>
+      <c r="AI256" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="31" t="inlineStr">
@@ -31041,6 +32572,12 @@
       <c r="AH257" s="55" t="n">
         <v>70</v>
       </c>
+      <c r="AI257" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="258" ht="28" customHeight="1">
       <c r="A258" s="28" t="inlineStr">
@@ -31158,6 +32695,12 @@
       </c>
       <c r="AH258" s="55" t="n">
         <v>167</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="259">
@@ -31273,6 +32816,12 @@
       <c r="AH259" s="55" t="n">
         <v>97</v>
       </c>
+      <c r="AI259" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="28" t="inlineStr">
@@ -31387,6 +32936,12 @@
       <c r="AH260" s="55" t="n">
         <v>83</v>
       </c>
+      <c r="AI260" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="31" t="inlineStr">
@@ -31505,6 +33060,12 @@
       <c r="AH261" s="55" t="n">
         <v>59</v>
       </c>
+      <c r="AI261" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="28" t="inlineStr">
@@ -31622,6 +33183,12 @@
       </c>
       <c r="AH262" s="55" t="n">
         <v>63</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="263">
@@ -31737,6 +33304,12 @@
       <c r="AH263" s="55" t="n">
         <v>57</v>
       </c>
+      <c r="AI263" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="28" t="inlineStr">
@@ -31851,6 +33424,12 @@
       <c r="AH264" s="55" t="n">
         <v>21</v>
       </c>
+      <c r="AI264" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="31" t="inlineStr">
@@ -31965,6 +33544,12 @@
       <c r="AH265" s="55" t="n">
         <v>27</v>
       </c>
+      <c r="AI265" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="28" t="inlineStr">
@@ -32079,6 +33664,12 @@
       <c r="AH266" s="55" t="n">
         <v>52</v>
       </c>
+      <c r="AI266" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>0.79</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="31" t="inlineStr">
@@ -32197,6 +33788,12 @@
       <c r="AH267" s="55" t="n">
         <v>83</v>
       </c>
+      <c r="AI267" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>0.57</v>
+      </c>
     </row>
     <row r="268" ht="28" customHeight="1">
       <c r="A268" s="28" t="inlineStr">
@@ -32314,6 +33911,12 @@
       </c>
       <c r="AH268" s="55" t="n">
         <v>85</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="269">
@@ -32429,6 +34032,12 @@
       <c r="AH269" s="55" t="n">
         <v>98</v>
       </c>
+      <c r="AI269" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>0.68</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="28" t="inlineStr">
@@ -32543,6 +34152,12 @@
       <c r="AH270" s="55" t="n">
         <v>99</v>
       </c>
+      <c r="AI270" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="31" t="inlineStr">
@@ -32657,6 +34272,12 @@
       <c r="AH271" s="55" t="n">
         <v>6</v>
       </c>
+      <c r="AI271" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="28" t="inlineStr">
@@ -32771,6 +34392,12 @@
       <c r="AH272" s="55" t="n">
         <v>67</v>
       </c>
+      <c r="AI272" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="31" t="inlineStr">
@@ -32885,6 +34512,12 @@
       <c r="AH273" s="55" t="n">
         <v>66</v>
       </c>
+      <c r="AI273" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="274" ht="28" customHeight="1">
       <c r="A274" s="28" t="inlineStr">
@@ -33002,6 +34635,12 @@
       </c>
       <c r="AH274" s="55" t="n">
         <v>122</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="275">
@@ -33117,6 +34756,12 @@
       <c r="AH275" s="55" t="n">
         <v>10</v>
       </c>
+      <c r="AI275" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="28" t="inlineStr">
@@ -33231,6 +34876,12 @@
       <c r="AH276" s="55" t="n">
         <v>126</v>
       </c>
+      <c r="AI276" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="31" t="inlineStr">
@@ -33345,6 +34996,12 @@
       <c r="AH277" s="55" t="n">
         <v>94</v>
       </c>
+      <c r="AI277" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AJ277" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="28" t="inlineStr">
@@ -33459,6 +35116,12 @@
       <c r="AH278" s="55" t="n">
         <v>134</v>
       </c>
+      <c r="AI278" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ278" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="31" t="inlineStr">
@@ -33573,6 +35236,12 @@
       <c r="AH279" s="55" t="n">
         <v>22</v>
       </c>
+      <c r="AI279" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AJ279" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="28" t="inlineStr">
@@ -33690,6 +35359,12 @@
       </c>
       <c r="AH280" s="55" t="n">
         <v>112</v>
+      </c>
+      <c r="AI280" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -33805,6 +35480,12 @@
       <c r="AH281" s="55" t="n">
         <v>171</v>
       </c>
+      <c r="AI281" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ281" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="28" t="inlineStr">
@@ -33919,6 +35600,12 @@
       <c r="AH282" s="55" t="n">
         <v>160</v>
       </c>
+      <c r="AI282" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AJ282" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="31" t="inlineStr">
@@ -34033,6 +35720,12 @@
       <c r="AH283" s="55" t="n">
         <v>30</v>
       </c>
+      <c r="AI283" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AJ283" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="284" ht="28" customHeight="1">
       <c r="A284" s="28" t="inlineStr">
@@ -34150,6 +35843,12 @@
       </c>
       <c r="AH284" s="55" t="n">
         <v>136</v>
+      </c>
+      <c r="AI284" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ284" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="285">
@@ -34265,6 +35964,12 @@
       <c r="AH285" s="55" t="n">
         <v>78</v>
       </c>
+      <c r="AI285" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ285" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="28" t="inlineStr">
@@ -34379,6 +36084,12 @@
       <c r="AH286" s="55" t="n">
         <v>152</v>
       </c>
+      <c r="AI286" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ286" t="n">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="287" ht="28" customHeight="1">
       <c r="A287" s="31" t="inlineStr">
@@ -34496,6 +36207,12 @@
       </c>
       <c r="AH287" s="55" t="n">
         <v>21</v>
+      </c>
+      <c r="AI287" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ287" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="288">
@@ -34611,6 +36328,12 @@
       <c r="AH288" s="55" t="n">
         <v>59</v>
       </c>
+      <c r="AI288" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="31" t="inlineStr">
@@ -34725,6 +36448,12 @@
       <c r="AH289" s="55" t="n">
         <v>90</v>
       </c>
+      <c r="AI289" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="28" t="inlineStr">
@@ -34839,6 +36568,12 @@
       <c r="AH290" s="55" t="n">
         <v>17</v>
       </c>
+      <c r="AI290" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="31" t="inlineStr">
@@ -34953,6 +36688,12 @@
       <c r="AH291" s="55" t="n">
         <v>85</v>
       </c>
+      <c r="AI291" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="28" t="inlineStr">
@@ -35067,6 +36808,12 @@
       <c r="AH292" s="55" t="n">
         <v>94</v>
       </c>
+      <c r="AI292" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AJ292" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="31" t="inlineStr">
@@ -35181,6 +36928,12 @@
       <c r="AH293" s="55" t="n">
         <v>9</v>
       </c>
+      <c r="AI293" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ293" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="28" t="inlineStr">
@@ -35295,6 +37048,12 @@
       <c r="AH294" s="55" t="n">
         <v>31</v>
       </c>
+      <c r="AI294" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ294" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="31" t="inlineStr">
@@ -35409,6 +37168,12 @@
       <c r="AH295" s="55" t="n">
         <v>115</v>
       </c>
+      <c r="AI295" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="28" t="inlineStr">
@@ -35526,6 +37291,12 @@
       </c>
       <c r="AH296" s="55" t="n">
         <v>109</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AJ296" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="297">
@@ -35641,6 +37412,12 @@
       <c r="AH297" s="55" t="n">
         <v>156</v>
       </c>
+      <c r="AI297" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AJ297" t="n">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="28" t="inlineStr">
@@ -35755,6 +37532,12 @@
       <c r="AH298" s="55" t="n">
         <v>173</v>
       </c>
+      <c r="AI298" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AJ298" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="299" ht="28" customHeight="1">
       <c r="A299" s="31" t="inlineStr">
@@ -35872,6 +37655,12 @@
       </c>
       <c r="AH299" s="55" t="n">
         <v>64</v>
+      </c>
+      <c r="AI299" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AJ299" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="300">
@@ -35987,6 +37776,12 @@
       <c r="AH300" s="55" t="n">
         <v>109</v>
       </c>
+      <c r="AI300" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ300" t="n">
+        <v>0.39</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="31" t="inlineStr">
@@ -36101,6 +37896,12 @@
       <c r="AH301" s="55" t="n">
         <v>91</v>
       </c>
+      <c r="AI301" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AJ301" t="n">
+        <v>0.62</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="28" t="inlineStr">
@@ -36215,6 +38016,12 @@
       <c r="AH302" s="55" t="n">
         <v>100</v>
       </c>
+      <c r="AI302" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ302" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="31" t="inlineStr">
@@ -36329,6 +38136,12 @@
       <c r="AH303" s="55" t="n">
         <v>156</v>
       </c>
+      <c r="AI303" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="28" t="inlineStr">
@@ -36443,6 +38256,12 @@
       <c r="AH304" s="55" t="n">
         <v>103</v>
       </c>
+      <c r="AI304" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="31" t="inlineStr">
@@ -36557,6 +38376,12 @@
       <c r="AH305" s="55" t="n">
         <v>144</v>
       </c>
+      <c r="AI305" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ305" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="28" t="inlineStr">
@@ -36671,6 +38496,12 @@
       <c r="AH306" s="55" t="n">
         <v>105</v>
       </c>
+      <c r="AI306" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="31" t="inlineStr">
@@ -36785,6 +38616,12 @@
       <c r="AH307" s="55" t="n">
         <v>101</v>
       </c>
+      <c r="AI307" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="28" t="inlineStr">
@@ -36899,6 +38736,12 @@
       <c r="AH308" s="55" t="n">
         <v>136</v>
       </c>
+      <c r="AI308" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AJ308" t="n">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="309" ht="28" customHeight="1">
       <c r="A309" s="31" t="inlineStr">
@@ -37016,6 +38859,12 @@
       </c>
       <c r="AH309" s="55" t="n">
         <v>65</v>
+      </c>
+      <c r="AI309" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AJ309" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="310">
@@ -37131,6 +38980,12 @@
       <c r="AH310" s="55" t="n">
         <v>82</v>
       </c>
+      <c r="AI310" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AJ310" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="31" t="inlineStr">
@@ -37245,6 +39100,12 @@
       <c r="AH311" s="55" t="n">
         <v>11</v>
       </c>
+      <c r="AI311" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>0.73</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="28" t="inlineStr">
@@ -37359,6 +39220,12 @@
       <c r="AH312" s="55" t="n">
         <v>116</v>
       </c>
+      <c r="AI312" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ312" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="31" t="inlineStr">
@@ -37473,6 +39340,12 @@
       <c r="AH313" s="55" t="n">
         <v>169</v>
       </c>
+      <c r="AI313" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ313" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="28" t="inlineStr">
@@ -37587,6 +39460,12 @@
       <c r="AH314" s="55" t="n">
         <v>64</v>
       </c>
+      <c r="AI314" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AJ314" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="31" t="inlineStr">
@@ -37701,6 +39580,12 @@
       <c r="AH315" s="55" t="n">
         <v>171</v>
       </c>
+      <c r="AI315" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="28" t="inlineStr">
@@ -37815,6 +39700,12 @@
       <c r="AH316" s="55" t="n">
         <v>69</v>
       </c>
+      <c r="AI316" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="31" t="inlineStr">
@@ -37929,6 +39820,12 @@
       <c r="AH317" s="55" t="n">
         <v>48</v>
       </c>
+      <c r="AI317" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="34" t="inlineStr">
@@ -38049,6 +39946,12 @@
       <c r="AH318" s="55" t="n">
         <v>113</v>
       </c>
+      <c r="AI318" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AJ318" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="37" t="inlineStr">
@@ -38169,6 +40072,12 @@
       <c r="AH319" s="55" t="n">
         <v>29</v>
       </c>
+      <c r="AI319" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AJ319" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="34" t="inlineStr">
@@ -38293,6 +40202,12 @@
       <c r="AH320" s="55" t="n">
         <v>102</v>
       </c>
+      <c r="AI320" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AJ320" t="n">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="37" t="inlineStr">
@@ -38413,6 +40328,12 @@
       <c r="AH321" s="55" t="n">
         <v>166</v>
       </c>
+      <c r="AI321" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AJ321" t="n">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="34" t="inlineStr">
@@ -38533,6 +40454,12 @@
       <c r="AH322" s="55" t="n">
         <v>23</v>
       </c>
+      <c r="AI322" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AJ322" t="n">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="37" t="inlineStr">
@@ -38653,6 +40580,12 @@
       <c r="AH323" s="55" t="n">
         <v>46</v>
       </c>
+      <c r="AI323" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AJ323" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="34" t="inlineStr">
@@ -38773,6 +40706,12 @@
       <c r="AH324" s="55" t="n">
         <v>75</v>
       </c>
+      <c r="AI324" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AJ324" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="37" t="inlineStr">
@@ -38893,6 +40832,12 @@
       <c r="AH325" s="55" t="n">
         <v>130</v>
       </c>
+      <c r="AI325" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AJ325" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="34" t="inlineStr">
@@ -39013,6 +40958,12 @@
       <c r="AH326" s="55" t="n">
         <v>116</v>
       </c>
+      <c r="AI326" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AJ326" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="37" t="inlineStr">
@@ -39133,6 +41084,12 @@
       <c r="AH327" s="55" t="n">
         <v>154</v>
       </c>
+      <c r="AI327" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ327" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="34" t="inlineStr">
@@ -39253,6 +41210,12 @@
       <c r="AH328" s="55" t="n">
         <v>42</v>
       </c>
+      <c r="AI328" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AJ328" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="37" t="inlineStr">
@@ -39373,6 +41336,12 @@
       <c r="AH329" s="55" t="n">
         <v>146</v>
       </c>
+      <c r="AI329" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AJ329" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="34" t="inlineStr">
@@ -39493,6 +41462,12 @@
       <c r="AH330" s="55" t="n">
         <v>107</v>
       </c>
+      <c r="AI330" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ330" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="37" t="inlineStr">
@@ -39613,6 +41588,12 @@
       <c r="AH331" s="55" t="n">
         <v>95</v>
       </c>
+      <c r="AI331" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AJ331" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="332" ht="28" customHeight="1">
       <c r="A332" s="34" t="inlineStr">
@@ -39737,6 +41718,12 @@
       <c r="AH332" s="55" t="n">
         <v>141</v>
       </c>
+      <c r="AI332" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AJ332" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="37" t="inlineStr">
@@ -39857,6 +41844,12 @@
       <c r="AH333" s="55" t="n">
         <v>22</v>
       </c>
+      <c r="AI333" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AJ333" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="34" t="inlineStr">
@@ -39977,6 +41970,12 @@
       <c r="AH334" s="55" t="n">
         <v>54</v>
       </c>
+      <c r="AI334" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AJ334" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="37" t="inlineStr">
@@ -40097,6 +42096,12 @@
       <c r="AH335" s="55" t="n">
         <v>20</v>
       </c>
+      <c r="AI335" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AJ335" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="34" t="inlineStr">
@@ -40217,6 +42222,12 @@
       <c r="AH336" s="55" t="n">
         <v>168</v>
       </c>
+      <c r="AI336" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AJ336" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="37" t="inlineStr">
@@ -40337,6 +42348,12 @@
       <c r="AH337" s="55" t="n">
         <v>91</v>
       </c>
+      <c r="AI337" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AJ337" t="n">
+        <v>0.73</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="34" t="inlineStr">
@@ -40457,6 +42474,12 @@
       <c r="AH338" s="55" t="n">
         <v>48</v>
       </c>
+      <c r="AI338" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AJ338" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="37" t="inlineStr">
@@ -40577,6 +42600,12 @@
       <c r="AH339" s="55" t="n">
         <v>94</v>
       </c>
+      <c r="AI339" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AJ339" t="n">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="34" t="inlineStr">
@@ -40697,6 +42726,12 @@
       <c r="AH340" s="55" t="n">
         <v>134</v>
       </c>
+      <c r="AI340" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AJ340" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="37" t="inlineStr">
@@ -40817,6 +42852,12 @@
       <c r="AH341" s="55" t="n">
         <v>136</v>
       </c>
+      <c r="AI341" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ341" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="34" t="inlineStr">
@@ -40937,6 +42978,12 @@
       <c r="AH342" s="55" t="n">
         <v>26</v>
       </c>
+      <c r="AI342" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AJ342" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="37" t="inlineStr">
@@ -41057,6 +43104,12 @@
       <c r="AH343" s="55" t="n">
         <v>154</v>
       </c>
+      <c r="AI343" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ343" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="34" t="inlineStr">
@@ -41177,6 +43230,12 @@
       <c r="AH344" s="55" t="n">
         <v>59</v>
       </c>
+      <c r="AI344" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AJ344" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="37" t="inlineStr">
@@ -41297,6 +43356,12 @@
       <c r="AH345" s="55" t="n">
         <v>143</v>
       </c>
+      <c r="AI345" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AJ345" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="34" t="inlineStr">
@@ -41417,6 +43482,12 @@
       <c r="AH346" s="55" t="n">
         <v>75</v>
       </c>
+      <c r="AI346" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AJ346" t="n">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="37" t="inlineStr">
@@ -41537,6 +43608,12 @@
       <c r="AH347" s="55" t="n">
         <v>9</v>
       </c>
+      <c r="AI347" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AJ347" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="34" t="inlineStr">
@@ -41657,6 +43734,12 @@
       <c r="AH348" s="55" t="n">
         <v>93</v>
       </c>
+      <c r="AI348" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AJ348" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="37" t="inlineStr">
@@ -41777,6 +43860,12 @@
       <c r="AH349" s="55" t="n">
         <v>17</v>
       </c>
+      <c r="AI349" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ349" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="34" t="inlineStr">
@@ -41897,6 +43986,12 @@
       <c r="AH350" s="55" t="n">
         <v>115</v>
       </c>
+      <c r="AI350" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AJ350" t="n">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="37" t="inlineStr">
@@ -42021,6 +44116,12 @@
       <c r="AH351" s="55" t="n">
         <v>20</v>
       </c>
+      <c r="AI351" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ351" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="352" ht="28" customHeight="1">
       <c r="A352" s="34" t="inlineStr">
@@ -42145,6 +44246,12 @@
       <c r="AH352" s="55" t="n">
         <v>4</v>
       </c>
+      <c r="AI352" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AJ352" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="37" t="inlineStr">
@@ -42265,6 +44372,12 @@
       <c r="AH353" s="55" t="n">
         <v>54</v>
       </c>
+      <c r="AI353" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ353" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="34" t="inlineStr">
@@ -42385,6 +44498,12 @@
       <c r="AH354" s="55" t="n">
         <v>92</v>
       </c>
+      <c r="AI354" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AJ354" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="37" t="inlineStr">
@@ -42509,6 +44628,12 @@
       <c r="AH355" s="55" t="n">
         <v>94</v>
       </c>
+      <c r="AI355" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ355" t="n">
+        <v>0.39</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="34" t="inlineStr">
@@ -42629,6 +44754,12 @@
       <c r="AH356" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI356" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AJ356" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="37" t="inlineStr">
@@ -42753,6 +44884,12 @@
       <c r="AH357" s="55" t="n">
         <v>162</v>
       </c>
+      <c r="AI357" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ357" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="34" t="inlineStr">
@@ -42873,6 +45010,12 @@
       <c r="AH358" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI358" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AJ358" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="37" t="inlineStr">
@@ -42997,6 +45140,12 @@
       <c r="AH359" s="55" t="n">
         <v>177</v>
       </c>
+      <c r="AI359" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AJ359" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="34" t="inlineStr">
@@ -43117,6 +45266,12 @@
       <c r="AH360" s="55" t="n">
         <v>154</v>
       </c>
+      <c r="AI360" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AJ360" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="37" t="inlineStr">
@@ -43237,6 +45392,12 @@
       <c r="AH361" s="55" t="n">
         <v>1</v>
       </c>
+      <c r="AI361" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AJ361" t="n">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="362" ht="28" customHeight="1">
       <c r="A362" s="34" t="inlineStr">
@@ -43361,6 +45522,12 @@
       <c r="AH362" s="55" t="n">
         <v>46</v>
       </c>
+      <c r="AI362" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AJ362" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="363" ht="28" customHeight="1">
       <c r="A363" s="37" t="inlineStr">
@@ -43485,6 +45652,12 @@
       <c r="AH363" s="55" t="n">
         <v>97</v>
       </c>
+      <c r="AI363" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AJ363" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="34" t="inlineStr">
@@ -43609,6 +45782,12 @@
       <c r="AH364" s="55" t="n">
         <v>15</v>
       </c>
+      <c r="AI364" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AJ364" t="n">
+        <v>0.19</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="37" t="inlineStr">
@@ -43729,6 +45908,12 @@
       <c r="AH365" s="55" t="n">
         <v>1</v>
       </c>
+      <c r="AI365" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AJ365" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="34" t="inlineStr">
@@ -43849,6 +46034,12 @@
       <c r="AH366" s="55" t="n">
         <v>132</v>
       </c>
+      <c r="AI366" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AJ366" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="37" t="inlineStr">
@@ -43969,6 +46160,12 @@
       <c r="AH367" s="55" t="n">
         <v>1</v>
       </c>
+      <c r="AI367" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AJ367" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="34" t="inlineStr">
@@ -44093,6 +46290,12 @@
       <c r="AH368" s="55" t="n">
         <v>151</v>
       </c>
+      <c r="AI368" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AJ368" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="37" t="inlineStr">
@@ -44217,6 +46420,12 @@
       <c r="AH369" s="55" t="n">
         <v>100</v>
       </c>
+      <c r="AI369" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ369" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="34" t="inlineStr">
@@ -44337,6 +46546,12 @@
       <c r="AH370" s="55" t="n">
         <v>87</v>
       </c>
+      <c r="AI370" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AJ370" t="n">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="37" t="inlineStr">
@@ -44457,6 +46672,12 @@
       <c r="AH371" s="55" t="n">
         <v>82</v>
       </c>
+      <c r="AI371" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ371" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="34" t="inlineStr">
@@ -44577,6 +46798,12 @@
       <c r="AH372" s="55" t="n">
         <v>172</v>
       </c>
+      <c r="AI372" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ372" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="37" t="inlineStr">
@@ -44697,6 +46924,12 @@
       <c r="AH373" s="55" t="n">
         <v>100</v>
       </c>
+      <c r="AI373" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ373" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="34" t="inlineStr">
@@ -44817,6 +47050,12 @@
       <c r="AH374" s="55" t="n">
         <v>93</v>
       </c>
+      <c r="AI374" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AJ374" t="n">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="37" t="inlineStr">
@@ -44937,6 +47176,12 @@
       <c r="AH375" s="55" t="n">
         <v>21</v>
       </c>
+      <c r="AI375" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AJ375" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="34" t="inlineStr">
@@ -45057,6 +47302,12 @@
       <c r="AH376" s="55" t="n">
         <v>19</v>
       </c>
+      <c r="AI376" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ376" t="n">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="37" t="inlineStr">
@@ -45177,6 +47428,12 @@
       <c r="AH377" s="55" t="n">
         <v>68</v>
       </c>
+      <c r="AI377" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ377" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="34" t="inlineStr">
@@ -45297,6 +47554,12 @@
       <c r="AH378" s="55" t="n">
         <v>62</v>
       </c>
+      <c r="AI378" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AJ378" t="n">
+        <v>0.38</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="37" t="inlineStr">
@@ -45417,6 +47680,12 @@
       <c r="AH379" s="55" t="n">
         <v>102</v>
       </c>
+      <c r="AI379" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AJ379" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="34" t="inlineStr">
@@ -45537,6 +47806,12 @@
       <c r="AH380" s="55" t="n">
         <v>153</v>
       </c>
+      <c r="AI380" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AJ380" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="37" t="inlineStr">
@@ -45657,6 +47932,12 @@
       <c r="AH381" s="55" t="n">
         <v>74</v>
       </c>
+      <c r="AI381" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AJ381" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="382" ht="28" customHeight="1">
       <c r="A382" s="34" t="inlineStr">
@@ -45781,6 +48062,12 @@
       <c r="AH382" s="55" t="n">
         <v>90</v>
       </c>
+      <c r="AI382" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ382" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="37" t="inlineStr">
@@ -45901,6 +48188,12 @@
       <c r="AH383" s="55" t="n">
         <v>115</v>
       </c>
+      <c r="AI383" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AJ383" t="n">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="34" t="inlineStr">
@@ -46021,6 +48314,12 @@
       <c r="AH384" s="55" t="n">
         <v>168</v>
       </c>
+      <c r="AI384" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AJ384" t="n">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="37" t="inlineStr">
@@ -46141,6 +48440,12 @@
       <c r="AH385" s="55" t="n">
         <v>148</v>
       </c>
+      <c r="AI385" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AJ385" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="34" t="inlineStr">
@@ -46265,6 +48570,12 @@
       <c r="AH386" s="55" t="n">
         <v>94</v>
       </c>
+      <c r="AI386" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AJ386" t="n">
+        <v>0.57</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="37" t="inlineStr">
@@ -46385,6 +48696,12 @@
       <c r="AH387" s="55" t="n">
         <v>45</v>
       </c>
+      <c r="AI387" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ387" t="n">
+        <v>0.57</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="34" t="inlineStr">
@@ -46505,6 +48822,12 @@
       <c r="AH388" s="55" t="n">
         <v>108</v>
       </c>
+      <c r="AI388" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AJ388" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="37" t="inlineStr">
@@ -46625,6 +48948,12 @@
       <c r="AH389" s="55" t="n">
         <v>97</v>
       </c>
+      <c r="AI389" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AJ389" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="34" t="inlineStr">
@@ -46745,6 +49074,12 @@
       <c r="AH390" s="55" t="n">
         <v>104</v>
       </c>
+      <c r="AI390" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AJ390" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="37" t="inlineStr">
@@ -46865,6 +49200,12 @@
       <c r="AH391" s="55" t="n">
         <v>129</v>
       </c>
+      <c r="AI391" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ391" t="n">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="34" t="inlineStr">
@@ -46985,6 +49326,12 @@
       <c r="AH392" s="55" t="n">
         <v>34</v>
       </c>
+      <c r="AI392" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ392" t="n">
+        <v>0.26</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="37" t="inlineStr">
@@ -47105,6 +49452,12 @@
       <c r="AH393" s="55" t="n">
         <v>135</v>
       </c>
+      <c r="AI393" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AJ393" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="34" t="inlineStr">
@@ -47225,6 +49578,12 @@
       <c r="AH394" s="55" t="n">
         <v>115</v>
       </c>
+      <c r="AI394" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AJ394" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="37" t="inlineStr">
@@ -47345,6 +49704,12 @@
       <c r="AH395" s="55" t="n">
         <v>73</v>
       </c>
+      <c r="AI395" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AJ395" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="34" t="inlineStr">
@@ -47465,6 +49830,12 @@
       <c r="AH396" s="55" t="n">
         <v>117</v>
       </c>
+      <c r="AI396" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AJ396" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="37" t="inlineStr">
@@ -47585,6 +49956,12 @@
       <c r="AH397" s="55" t="n">
         <v>29</v>
       </c>
+      <c r="AI397" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AJ397" t="n">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="34" t="inlineStr">
@@ -47705,6 +50082,12 @@
       <c r="AH398" s="55" t="n">
         <v>25</v>
       </c>
+      <c r="AI398" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AJ398" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="37" t="inlineStr">
@@ -47825,6 +50208,12 @@
       <c r="AH399" s="55" t="n">
         <v>153</v>
       </c>
+      <c r="AI399" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ399" t="n">
+        <v>0.6899999999999999</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="34" t="inlineStr">
@@ -47945,6 +50334,12 @@
       <c r="AH400" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI400" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AJ400" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="37" t="inlineStr">
@@ -48065,6 +50460,12 @@
       <c r="AH401" s="55" t="n">
         <v>120</v>
       </c>
+      <c r="AI401" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AJ401" t="n">
+        <v>0.77</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="34" t="inlineStr">
@@ -48185,6 +50586,12 @@
       <c r="AH402" s="55" t="n">
         <v>113</v>
       </c>
+      <c r="AI402" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ402" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="37" t="inlineStr">
@@ -48305,6 +50712,12 @@
       <c r="AH403" s="55" t="n">
         <v>48</v>
       </c>
+      <c r="AI403" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ403" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="34" t="inlineStr">
@@ -48425,6 +50838,12 @@
       <c r="AH404" s="55" t="n">
         <v>138</v>
       </c>
+      <c r="AI404" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AJ404" t="n">
+        <v>0.51</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="37" t="inlineStr">
@@ -48545,6 +50964,12 @@
       <c r="AH405" s="55" t="n">
         <v>26</v>
       </c>
+      <c r="AI405" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ405" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="34" t="inlineStr">
@@ -48665,6 +51090,12 @@
       <c r="AH406" s="55" t="n">
         <v>13</v>
       </c>
+      <c r="AI406" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ406" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="37" t="inlineStr">
@@ -48785,6 +51216,12 @@
       <c r="AH407" s="55" t="n">
         <v>157</v>
       </c>
+      <c r="AI407" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AJ407" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="34" t="inlineStr">
@@ -48909,6 +51346,12 @@
       <c r="AH408" s="55" t="n">
         <v>74</v>
       </c>
+      <c r="AI408" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ408" t="n">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="37" t="inlineStr">
@@ -49029,6 +51472,12 @@
       <c r="AH409" s="55" t="n">
         <v>173</v>
       </c>
+      <c r="AI409" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AJ409" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="34" t="inlineStr">
@@ -49149,6 +51598,12 @@
       <c r="AH410" s="55" t="n">
         <v>0</v>
       </c>
+      <c r="AI410" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AJ410" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="37" t="inlineStr">
@@ -49269,6 +51724,12 @@
       <c r="AH411" s="55" t="n">
         <v>142</v>
       </c>
+      <c r="AI411" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AJ411" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="34" t="inlineStr">
@@ -49389,6 +51850,12 @@
       <c r="AH412" s="55" t="n">
         <v>72</v>
       </c>
+      <c r="AI412" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ412" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="37" t="inlineStr">
@@ -49509,6 +51976,12 @@
       <c r="AH413" s="55" t="n">
         <v>23</v>
       </c>
+      <c r="AI413" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AJ413" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="34" t="inlineStr">
@@ -49629,6 +52102,12 @@
       <c r="AH414" s="55" t="n">
         <v>108</v>
       </c>
+      <c r="AI414" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ414" t="n">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="37" t="inlineStr">
@@ -49749,6 +52228,12 @@
       <c r="AH415" s="55" t="n">
         <v>82</v>
       </c>
+      <c r="AI415" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AJ415" t="n">
+        <v>0.5600000000000001</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="34" t="inlineStr">
@@ -49873,6 +52358,12 @@
       <c r="AH416" s="55" t="n">
         <v>50</v>
       </c>
+      <c r="AI416" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AJ416" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="37" t="inlineStr">
@@ -49993,6 +52484,12 @@
       <c r="AH417" s="55" t="n">
         <v>38</v>
       </c>
+      <c r="AI417" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AJ417" t="n">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="34" t="inlineStr">
@@ -50113,6 +52610,12 @@
       <c r="AH418" s="55" t="n">
         <v>11</v>
       </c>
+      <c r="AI418" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AJ418" t="n">
+        <v>0.71</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="37" t="inlineStr">
@@ -50233,6 +52736,12 @@
       <c r="AH419" s="55" t="n">
         <v>123</v>
       </c>
+      <c r="AI419" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AJ419" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="34" t="inlineStr">
@@ -50357,6 +52866,12 @@
       <c r="AH420" s="55" t="n">
         <v>108</v>
       </c>
+      <c r="AI420" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AJ420" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="37" t="inlineStr">
@@ -50477,7 +52992,14 @@
       <c r="AH421" s="55" t="n">
         <v>72</v>
       </c>
+      <c r="AI421" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ421" t="n">
+        <v>0.63</v>
+      </c>
     </row>
+    <row r="422"/>
   </sheetData>
   <autoFilter ref="A4:Y4"/>
   <mergeCells count="8">
